--- a/docs/hr/HR_Task_Tracker_Oct2026.xlsx
+++ b/docs/hr/HR_Task_Tracker_Oct2026.xlsx
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterTasks" displayName="MasterTasks" ref="A1:M78" headerRowCount="1">
-  <autoFilter ref="A1:M78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterTasks" displayName="MasterTasks" ref="A1:M107" headerRowCount="1">
+  <autoFilter ref="A1:M107"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Category"/>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PendingTasks" displayName="PendingTasks" ref="A1:M55" headerRowCount="1">
-  <autoFilter ref="A1:M55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PendingTasks" displayName="PendingTasks" ref="A1:M83" headerRowCount="1">
+  <autoFilter ref="A1:M83"/>
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Category"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RRAdditions" displayName="RRAdditions" ref="A1:D21" headerRowCount="1">
-  <autoFilter ref="A1:D21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RRAdditions" displayName="RRAdditions" ref="A1:D27" headerRowCount="1">
+  <autoFilter ref="A1:D27"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Role"/>
     <tableColumn id="2" name="Responsibility"/>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Report started (previous-day format approved 23 Sep). 14 Oct report covered only 30 employees; MKCD: 'Total employees 41. I do not want any reasons.' Drivers to be covered via a register.</t>
+          <t>Report started (previous-day format approved 23 Sep). 14 Oct report covered only 30 employees; MKCD: 'Total employees 41. I do not want any reasons.' Drivers to be covered via a register. Also ClickUp 14yp17znrwc (live performance dashboard).</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R&amp;R mails done for some (ClickUp: telecaller R&amp;R Jan 2026, all-employee R&amp;R Jun 2026). Targets in writing still missing - MKCD on 11 Oct: 'No one should say I didn't know my target'.</t>
+          <t>R&amp;R mails done for some (ClickUp: telecaller R&amp;R Jan 2026, all-employee R&amp;R Jun 2026). Targets in writing still missing - MKCD on 11 Oct: 'No one should say I didn't know my target'. Also ClickUp 14yp17zk7xe (measurable targets for every role) and 14yp17zkpzz (departmental goals cascade).</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Policy stated repeatedly; telecaller proportional pay applied partly (Apr-May). Not yet systematic for all employees.</t>
+          <t>Policy stated repeatedly; telecaller proportional pay applied partly (Apr-May). Not yet systematic for all employees. Also ClickUp 14yp17zmem1 (performance-linked pay one-to-one).</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>'More than 10 reminders' per MKCD (23 Oct). Gnaneshwar proposed 0.5-day penalty per miss (12 Oct). Still many employees not using software (23 Oct).</t>
+          <t>'More than 10 reminders' per MKCD (23 Oct). Gnaneshwar proposed 0.5-day penalty per miss (12 Oct). Still many employees not using software (23 Oct). Also ClickUp 14yp17zk7xf (ClickUp time tracking mandatory).</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1673,9 +1673,9 @@
           <t>Gnaneshwar (HR Executive)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar: 'tomorrow I will provide access'. No confirmation.</t>
+          <t>Gnaneshwar: 'tomorrow I will provide access'. ClickUp task 14yp17zxpg9 marked complete by Gnaneshwar on 27 Oct 2026.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1698,11 +1698,7 @@
           <t>Confirm all staff enrolled; maintain access list.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1926,7 +1922,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>ClickUp 'CSR Executive Recruitment' in progress since Dec 2025; no hire.</t>
+          <t>ClickUp 'CSR Executive Recruitment' in progress since Dec 2025; no hire. Also ClickUp 14yp17zmepb (BDM recruitment).</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Deva Reddy joined; trained in Hyderabad 29 Sep; left for Bangalore 3 Oct.</t>
+          <t>Deva Reddy joined; trained in Hyderabad 29 Sep; left for Bangalore 3 Oct. 25 Oct: MKCD directs closure of the Bengaluru office and this position - see I10.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2433,7 +2429,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Venu Gopal joined Dec 2025.</t>
+          <t>Venu Gopal joined Dec 2025. 25 Oct: MKCD's view is to terminate Venugopal for low output - see I11.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2645,7 +2641,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17 employees on RGI on-roll (22 Oct). MKCD preparing trust-wise list (Org Structure sheet Sep 2026 has 'New Trust from Oct 2026' column). Satish -&gt; consultant on HKM Hyd (MKCD to confirm). Veda Vittama's wife -&gt; trust TBD.</t>
+          <t>17 employees on RGI on-roll (22 Oct). MKCD preparing trust-wise list (Org Structure sheet Sep 2026 has 'New Trust from Oct 2026' column). Satish -&gt; consultant on HKM Hyd (MKCD to confirm). Veda Vittama's wife -&gt; trust TBD. Also ClickUp 14yp17zk7x4 (allocate each employee to a trust).</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2704,7 +2700,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Naveen V shifted to RGIL (email 10 Oct). Himanshu - no confirmation (org sheet suggests HKM India).</t>
+          <t>Naveen V shifted to RGIL (email 10 Oct). Himanshu - no confirmation (org sheet suggests HKM India). 25 Oct: Himanshu move approved 12 Oct; payroll + PF paperwork pending - see J11.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3258,7 +3254,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'she should be on-boarded on payroll as Tele Caller, CTC and trust I will confirm'. No further update.</t>
+          <t>MKCD: 'she should be on-boarded on payroll as Tele Caller, CTC and trust I will confirm'. No further update. 25 Oct: MKCD prefers event-based consultant for Junjunu Mataji instead of full-time - see J10.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3828,7 +3824,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'I will update after 2 days. Mostly Satish will be consultant in HKM Hyderabad trust'.</t>
+          <t>MKCD: 'I will update after 2 days. Mostly Satish will be consultant in HKM Hyderabad trust'. Consultancy agreement and KT still open - see I2.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3887,7 +3883,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>RP 8 Sep: 'will sit with STDD and conclude'. Shashank &amp; Sai Sharath terminated 17 Sep (org sheet). No written conclusion to MKCD.</t>
+          <t>RP 8 Sep: 'will sit with STDD and conclude'. Shashank &amp; Sai Sharath terminated 17 Sep (org sheet). No written conclusion to MKCD. 25 Oct: October salary strictly proportionate to performance for all telecallers - see J8.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4905,7 +4901,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>RP called twice, no response (7 Oct). No closure.</t>
+          <t>RP called twice, no response (7 Oct). No closure. 25 Oct: no October salary; lower package / different role on rejoining - see J3.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -5023,7 +5019,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Meeting held 16 Oct; no written outcome.</t>
+          <t>Meeting held 16 Oct; no written outcome. 25 Oct decisions recorded in J4 (Prema Rupa), J7 (Sudhakar), J10 (Sashikanta).</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -5082,7 +5078,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>RP: 'Ok I will inform Sai'.</t>
+          <t>RP: 'Ok I will inform Sai'. 25 Oct: did not attend in October - no October salary; see J2.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -5145,6 +5141,1685 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Replacement for Lingala Sai Sharath (donation telecaller, last working day 31 Oct) and hand-over of his positive donor leads to Sai Vardhan / Sharavan.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc (25 Oct 2026) B2</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Hand-over requested 15 Oct; no replacement sourced yet.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>RP: start sourcing; GN: collect lead hand-over sheet from Sharath before 31 Oct.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Satish Maddela consultancy agreement (Mondays on site; movie-editing scope, fee, IP) - pending with HR since 24 Oct. STDD to negotiate Rs 25,000/month (Rs 50,000 asked for 1-2 days a month is too costly); else end. October payment on hold. Satish -&gt; Praveen knowledge transfer and documentation.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B3 + G2; ClickUp 14yp17zk7xa / 14yp17zk7x9 / 14yp17zk7x6</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Agreement not drafted. Graphics lead role formally with Praveen meanwhile.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>RP: draft agreement at the negotiated fee or issue closure letter; confirm KT completed.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Social-media executive vacancy (Akhil left 17 Oct) - now covered by Venkatesh (PPC). MKCD to decide whether to still hire; HR to close or open the requisition accordingly. Akhil PIP task in ClickUp is obsolete - close it.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B4 / A5; ClickUp 14yp17zmenz (Akhil PIP)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Sep-2026 plan listed a Social Media Manager.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision by 15 Nov; GN to close ClickUp task 14yp17zmenz.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Roster integrity: confirm employment status of Anji (auto driver), P Ravi Kumar, Vinod Singh Thakur and the holder of the MKCP Assistant desk account (missing from the 24 Oct HR roster); also add Junjunu Mataji and Radha Giridhari records (paid but not in roster). P Ravi Kumar responsibilities / KT and the 2 pm meeting with HR to be concluded.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B6, G14, G16; ClickUp 14yp17zmep3 / 14yp17zmep2</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Roster of 42 rows (24 Oct) excludes these names.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>GN: reconcile roster vs pay sheets of all trusts; one row per paid person.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Settle department placement of Sashikanta Sahoo, Prema Rupa Dasa, Sonayla Sudhakar, Yankiral Shiv Raj, Purushottam Sharma, P Srilakshmi Sailaja, Gaddam Sai Kiran (sources disagree); record accountant V Naveen Kumar as Yatra dept (TRIDAS/TSF accounts) or Hanuma's transfer to Yatra once HG LKP agrees. Then update master roster, Whimsical org board and department docs.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B7, A1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>MKCD + STDD decision pending (due 7 Nov).</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>RP: prepare the placement sheet with recommendation for MKCD/STDD; GN: update roster/docs after decision.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Collect dates of joining for all staff from Keka / GreytHR into the employee living documents (only 4 confirmed) and link every employee living doc from the Notion Leadership Hub and the HR roster sheet.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B8, D3</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>GN: export DOJ list from Keka; add to each doc; add links column in roster sheet.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Daily-report &amp; ClickUp compliance specifics: Nama Prabhu Dasa, Bala Mukunda Dasa, Banusundar irregular; Sai Vardhan to start ClickUp from 1 Nov; Revanth, Amit Mondal, Madhu Mangal, Hanumaya, Ramesh J, Purushottam, Chenna Reddy have no ClickUp / email (licence shortage) - buy licences or assign manager-maintained logs. ClickUp time tracking mandatory for all employees.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B9; ClickUp 14yp17zk7xf</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Licence shortage unresolved; see B2/B4.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>GN: licence count and cost to MKCD by 7 Nov; confirm Sai Vardhan live on ClickUp 1 Nov.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Decide which HR notes (performance flags) stay in the shared employee living documents vs a private HR tab.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B10</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Docs are shareable; performance notes currently inside them.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision; RP to then move confidential notes.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>I9</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>2026-27 recruitment plan (approx. 45 roles, approx. Rs 17.2 L/month) - re-prioritise against the budget; sequence: CSR BD manager + proposal writer, AI core team, yatra coordinators. Finalise manpower requirements per department. Tech / AI hiring (GenAI engineer, Platform lead, Data scientist, backend developer): JDs from SRRD, compensation range approval, posting, sourcing - hold until MKCD confirms priority.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B11; ClickUp 14yp17zp5xt / 5xr / 5xq / 5xp, 14yp17znrz3 / znrz1 / znryz, 14yp17zkq26 / zkq1q / zkq1r, 14yp17zmen3 / zmen2, 14yp17zmepa (CA-level accountant), MOM 86d3febu0</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Several duplicate hiring tasks open across ClickUp spaces; none progressing.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>RP: one consolidated hiring plan sheet (role, trust, CTC, priority, status) to MKCD by 10 Nov; GN: link/merge duplicate ClickUp tasks.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Close the Bengaluru office and the Bengaluru telecaller position (Deva Reddy): exit date, notice, asset return, lead hand-over; update Deva Reddy's doc and the Tele-sales dept doc.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc A4 (with HG LKP)</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Decision direction given 25 Oct; reverses recruitment item C11.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>RP: exit plan and notice draft for MKCD approval by 15 Nov.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Kanukuntla Venugopal (content writer): MKCD's view is terminate for low output (content to be AI-generated; postings moved to Venkatesh). HR to follow due process - performance record, notice.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc A5 / G3</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>In progress; not yet communicated to Venugopal.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>RP: performance record + notice draft; conclude with STDD.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>I12</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Org structure, department structure and a written role / designation / JD / CTC document for every person (PID39-42); lean team target &lt;= Rs 5 lakh/month; review web developer role at Rs 46k; department SPOC / role register; employee capability &amp; responsibility matrix; communicate the new structure to all staff. Oct-Dec 2026 deliverable in the People &amp; Operations plan.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Notion 'People &amp; Operations (Vertical Plan)'; ClickUp 14yp17zmek9, 14yp17zmeke, 14yp17zp7pf, 14yp17zk7xj, 14yp17zkpzz; MASTER register MA-00165</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Dept R&amp;R doc and employee living docs exist (Claude Docs, 24 Oct) - JDs/CTC not yet in them.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>RP: fill designation, JD and CTC for every person in the living docs; GN: capability matrix sheet.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>I13</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Backup employee for every role with knowledge-transfer plan (PID101); second-line names to confirm (Tele-sales, Yatra coordinator, ERP, accounts lead).</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Notion People &amp; Operations plan PID101; Claude Action Items doc B12</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>RP: backup column in the roster sheet, confirmed with each department head.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end recruitment &amp; onboarding SOP and onboarding kit (PID102); quarterly training calendar with in-house and external speakers (PID15/16, Jan-Mar 2027); written R&amp;R for Culture Connect; incorporate the GM/AVP promotion qualifying-criteria resolution into a formal promotion policy; re-recruit trained ex-employees under stricter SOPs where suitable.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Notion People &amp; Operations plan; ClickUp 14yp17znrx6; MASTER register MA-02102, MA-01735</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Planning stage.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>RP: SOP + promotion policy drafts to MKCD by 10 Nov; training calendar by Dec.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Employee monitoring software (laptops PID13, field executives PID14): trial and disclosure decision. Move performance-review ownership from HR to Operations (decision) and build the live performance dashboard.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp 14yp17zmepj, 14yp17znrwb, 14yp17znrwc; Notion PID13/14</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Decisions pending with MKCD.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision; GN to run the trial once approved.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>I16</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Email all staff on office hours, Sunday working and discipline rules (after-hours / spiritual-course time is not office hours; report at 10 am). Puri staff pilgrimage dates to be fixed with HR Manager. Prasadam contamination complaint to be closed with HR Manager.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp 14yp17zmep1, 14yp17zp0mr, 14yp17zp0mk</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Open in Arjun Prabhu / MKCP Assistant lists.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>RP: one circular on hours &amp; discipline; dates for Puri pilgrimage; complaint closure note.</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Verify and close stale HR tasks: Shashank termination notice (14yp17zmeny), TSF salary payments release (14yp17znrw1), PF withdrawal rules query from a kirtaniya (MASTER MA-00317), staff engagement planning review (MA-00919), volunteer details collection (MOM 86d3febpm).</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp MKCP Assistant list; MOM lists; MASTER register</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Status unknown; likely done or obsolete.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>GN: confirm each and close in ClickUp with a one-line comment.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>HR process: issue written warning emails for every non-performance / target-shortfall case (J2-J12) BEFORE the October payroll; keep copies in the employee files. Zero-performance employees: termination email to HR.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G27; ClickUp 14yp17zmem2</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Due 3 Nov 2026.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>RP: warning letters out by 3 Nov; list of letters issued to MKCD.</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Vikash Kumar (Senior Tele Sales Executive): flagged non-performer 4-5 months; did not attend in October - no October salary; on return salary proportionate to performance. Performance plan or exit.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B1, G21</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Earlier: WFH till Diwali (see H4).</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>RP: apply in October pay sheet; written notice.</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>B Sharavan Kumar: no October salary (absent all month, no leave balance); on rejoining a lower package and different role for a few months.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G10 (see H1)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Unapproved leave since early Oct.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>RP: pay sheet entry + letter.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Prema Rupa Dasa: no October salary (no performance for approx. 2 years despite warnings); rejoin only in a new role at a revised lower CTC - perform or exit.</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G12 (with Suguna Radha DD; see H3)</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Discussion with MKCD on 16 Oct.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>RP: pay sheet entry + revised-role letter.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Purushottam Sharma: stop salary - 1-1.5 months' leave taken without approval despite written refusal; resumes only on rejoining.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G25</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>RP: pay sheet entry + letter.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Kouloju Sumanth (SEO): terminate - no performance for weeks/months, excessive leave, conduct. Hem Chand takes over SEO.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G6</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>RP: termination due process with Hem Chand; final settlement.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Written serious warnings: Hem Chand Tunga (targets not taken seriously; clear months-old pending tasks or salary cut), Sonayla Sudhakar (salary proportionate to performance from October), Nagella Banusundar / Arjuna Bandhu Dasa (no log-in/log-out, no ClickUp, tasks pending; report at 10 am; must do tele-sales; training-attendance issue), Radha Giridhari (October salary cut with warning; behaviour must change).</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G5, G23, G20, G16; ClickUp 14yp17zp0mj</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>RP: four warning letters by 3 Nov; copies to MKCD.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>October salary strictly proportionate to performance for all telecallers (G Sai Kiran, Sai Sharath, Anthati Sai Kumar, Narsing Rao, Charan Kumar, Shiva Vara Prasad, Rajashekhar Reddy) with written warnings for shortfalls; Byreddy Saivardhan Reddy to prove performance this month (100% salary cannot continue while the team under-performs); A Faneendra Chary salary proportionate to own and team results.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G24, G17, G18 (see E9)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Target vs actual data from Sai Vardhan needed.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>RP + GN: October target-vs-actual per telecaller -&gt; pay sheet by 4 Nov.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>End consultant retainers of Aniket (DYGN Media) and Srinivas Mahankali immediately; redirect the cost to in-house full-time hires.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G26 (with STDD)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>RP: closure emails and final invoices; inform Finance.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Sashikanta Sahoo: fix R&amp;R in writing (housekeeping, purchases/stores/warehouse, kirtan-training organisation, watering plants - weekly duties - plus daily fundraising / telecalling and family visits). Junjunu Mataji (his wife): solid roadmap or move to event-based consultant paid per event (preferred) - supersedes the full-time telecaller onboarding in D12.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G13, G14 (with Suguna Radha DD)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>RP: written R&amp;R letter for Sashikanta; consultant terms for Junjunu Mataji for MKCD approval.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Himanshu Bisoyi trust movement TSF -&gt; HKM Hyderabad (approved 12 Oct): complete payroll and PF paperwork (no new budget).</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B5 (see D2)</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>RP: new appointment letter + PF transfer with Finance by 31 Oct.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL (MKCD + RP only): Gnaneshwar - termination for underperformance over many months to be discussed with HR Manager; document the performance record; confirm consistency with offer-letter terms and put in writing before the October payroll (5 Nov).</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G1; Gnaneshwar living doc 25 Oct note</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Not yet discussed with RP.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>MKCD + RP meeting before 5 Nov. Deliberately NOT created in ClickUp.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5160,7 +6835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5283,7 +6958,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Report started (previous-day format approved 23 Sep). 14 Oct report covered only 30 employees; MKCD: 'Total employees 41. I do not want any reasons.' Drivers to be covered via a register.</t>
+          <t>Report started (previous-day format approved 23 Sep). 14 Oct report covered only 30 employees; MKCD: 'Total employees 41. I do not want any reasons.' Drivers to be covered via a register. Also ClickUp 14yp17znrwc (live performance dashboard).</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -5342,7 +7017,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R&amp;R mails done for some (ClickUp: telecaller R&amp;R Jan 2026, all-employee R&amp;R Jun 2026). Targets in writing still missing - MKCD on 11 Oct: 'No one should say I didn't know my target'.</t>
+          <t>R&amp;R mails done for some (ClickUp: telecaller R&amp;R Jan 2026, all-employee R&amp;R Jun 2026). Targets in writing still missing - MKCD on 11 Oct: 'No one should say I didn't know my target'. Also ClickUp 14yp17zk7xe (measurable targets for every role) and 14yp17zkpzz (departmental goals cascade).</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -5519,7 +7194,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>'More than 10 reminders' per MKCD (23 Oct). Gnaneshwar proposed 0.5-day penalty per miss (12 Oct). Still many employees not using software (23 Oct).</t>
+          <t>'More than 10 reminders' per MKCD (23 Oct). Gnaneshwar proposed 0.5-day penalty per miss (12 Oct). Still many employees not using software (23 Oct). Also ClickUp 14yp17zk7xf (ClickUp time tracking mandatory).</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5661,17 +7336,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Performance &amp; Daily Reporting</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Adopt a performance-appraisal software (Keka or any standard tool) so appraisal data is captured in a system, not in Word/Excel.</t>
+          <t>HR process: issue written warning emails for every non-performance / target-shortfall case (J2-J12) BEFORE the October payroll; keep copies in the employee files. Zero-performance employees: termination email to HR.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -5686,22 +7361,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Group 6 Mar 2026, 24 Oct 2026</t>
+          <t>Claude Action Items doc G27; ClickUp 14yp17zmem2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>No tool selected. MKCD: 'there are so many softwares... please try to use any one of them'.</t>
+          <t>Due 3 Nov 2026.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Evaluate Keka Performance module (already a Keka customer) vs Zoho People; present recommendation + cost to MKCD.</t>
+          <t>RP: warning letters out by 3 Nov; list of letters issued to MKCD.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5720,47 +7395,47 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ClickUp &amp; Daily Report Discipline</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Help whole team work in ClickUp - Hem Chand to create users and train; buy extra ClickUp / Tally seats if needed; telecaller call minutes from Tata Tele software only.</t>
+          <t>October salary strictly proportionate to performance for all telecallers (G Sai Kiran, Sai Sharath, Anthati Sai Kumar, Narsing Rao, Charan Kumar, Shiva Vara Prasad, Rajashekhar Reddy) with written warnings for shortfalls; Byreddy Saivardhan Reddy to prove performance this month (100% salary cannot continue while the team under-performs); A Faneendra Chary salary proportionate to own and team results.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>URGENT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Group 24 Aug, 26 Jun, 23 Oct 2026</t>
+          <t>Claude Action Items doc G24, G17, G18 (see E9)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar task 'ClickUp and Tata Tele usage report' in progress (ClickUp 24 Oct).</t>
+          <t>Target vs actual data from Sai Vardhan needed.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>List employees without ClickUp seat / not logging; get seats added; send usage report weekly.</t>
+          <t>RP + GN: October target-vs-actual per telecaller -&gt; pay sheet by 4 Nov.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5779,17 +7454,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Performance &amp; Daily Reporting</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Recruit a go-getter Tele Sales Manager (fund-raising / NGO tele-sales background) to run the telecaller team.</t>
+          <t>Adopt a performance-appraisal software (Keka or any standard tool) so appraisal data is captured in a system, not in Word/Excel.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -5797,9 +7472,9 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5809,17 +7484,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Group 22 Nov 2025, 14 Mar, 16 May 2026</t>
+          <t>Group 6 Mar 2026, 24 Oct 2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>P Srilakshmi Sailaja onboarded Aug 2026 as Telesales Manager - WFH, Rs 30K fixed for 3 months, review after 3 months (Nov 2026).</t>
+          <t>No tool selected. MKCD: 'there are so many softwares... please try to use any one of them'.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3-month review due Nov 2026: performance data, decision on continuation / full-time role.</t>
+          <t>Evaluate Keka Performance module (already a Keka customer) vs Zoho People; present recommendation + cost to MKCD.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5838,27 +7513,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>ClickUp &amp; Daily Report Discipline</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Recruit Digital Marketing Manager.</t>
+          <t>Help whole team work in ClickUp - Hem Chand to create users and train; buy extra ClickUp / Tally seats if needed; telecaller call minutes from Tata Tele software only.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5868,17 +7543,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Group 16 May 2026</t>
+          <t>Group 24 Aug, 26 Jun, 23 Oct 2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>MKCD asked for update; none given.</t>
+          <t>Gnaneshwar task 'ClickUp and Tata Tele usage report' in progress (ClickUp 24 Oct).</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Status update: JD, postings, pipeline, shortlist date.</t>
+          <t>List employees without ClickUp seat / not logging; get seats added; send usage report weekly.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5897,7 +7572,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -5907,7 +7582,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Recruit Best PPC Expert (10+ years, high package acceptable).</t>
+          <t>Recruit a go-getter Tele Sales Manager (fund-raising / NGO tele-sales background) to run the telecaller team.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -5915,9 +7590,9 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5927,17 +7602,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Group 21 May 2026</t>
+          <t>Group 22 Nov 2025, 14 Mar, 16 May 2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>'We will look into this.' ClickUp 'PPC Recruitment' in progress since Mar 2026.</t>
+          <t>P Srilakshmi Sailaja onboarded Aug 2026 as Telesales Manager - WFH, Rs 30K fixed for 3 months, review after 3 months (Nov 2026).</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Status update with shortlisted profiles.</t>
+          <t>3-month review due Nov 2026: performance data, decision on continuation / full-time role.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5956,27 +7631,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Place every employee / consultant in the correct trust (HKM Hyd / HKM India / RGI / TSF) as per contribution; convert consultants to employees only after MKCD's trust-wise list.</t>
+          <t>Recruit Digital Marketing Manager.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5986,17 +7661,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Group 7 Sep, 22 Sep, 22 Oct 2026</t>
+          <t>Group 16 May 2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17 employees on RGI on-roll (22 Oct). MKCD preparing trust-wise list (Org Structure sheet Sep 2026 has 'New Trust from Oct 2026' column). Satish -&gt; consultant on HKM Hyd (MKCD to confirm). Veda Vittama's wife -&gt; trust TBD.</t>
+          <t>MKCD asked for update; none given.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MKCD to share final trust-wise list; HR to execute transfers, offer letters, PF/ESI mapping by 10 Nov.</t>
+          <t>Status update: JD, postings, pipeline, shortlist date.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,17 +7690,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Terminate / proportionally pay non-performing telecallers &amp; fund raisers after grace period; conclude with Shruthadev Prabhu.</t>
+          <t>Recruit Best PPC Expert (10+ years, high package acceptable).</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -6033,9 +7708,9 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -6045,17 +7720,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Group 4 &amp; 27 Dec 2025, 18 Mar, 3 May, 7-8 Sep 2026</t>
+          <t>Group 21 May 2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>RP 8 Sep: 'will sit with STDD and conclude'. Shashank &amp; Sai Sharath terminated 17 Sep (org sheet). No written conclusion to MKCD.</t>
+          <t>'We will look into this.' ClickUp 'PPC Recruitment' in progress since Mar 2026.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Send written list: who is retained / exited / on proportional pay, with data.</t>
+          <t>Status update with shortlisted profiles.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6074,27 +7749,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Engagement, Training &amp; Culture</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Personal mobile phone restriction policy in office (lockers / deposit) - discuss with MKCD next week and implement soon.</t>
+          <t>Place every employee / consultant in the correct trust (HKM Hyd / HKM India / RGI / TSF) as per contribution; convert consultants to employees only after MKCD's trust-wise list.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -6104,17 +7779,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Group 24 Oct 2026</t>
+          <t>Group 7 Sep, 22 Sep, 22 Oct 2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>RP: 'Sure Prabhuji'.</t>
+          <t>17 employees on RGI on-roll (22 Oct). MKCD preparing trust-wise list (Org Structure sheet Sep 2026 has 'New Trust from Oct 2026' column). Satish -&gt; consultant on HKM Hyd (MKCD to confirm). Veda Vittama's wife -&gt; trust TBD. Also ClickUp 14yp17zk7x4 (allocate each employee to a trust).</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Draft policy + meet MKCD week of 27 Oct.</t>
+          <t>MKCD to share final trust-wise list; HR to execute transfers, offer letters, PF/ESI mapping by 10 Nov.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6133,22 +7808,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Policies &amp; Documents</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Consolidated status of ALL tasks given via WhatsApp / email / meetings (file 'Tasks 2026 - Your Name') - and weekly pending-task update email to MKCD.</t>
+          <t>Terminate / proportionally pay non-performing telecallers &amp; fund raisers after grace period; conclude with Shruthadev Prabhu.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
+          <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6163,17 +7838,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Group 18 Aug 2025 ... 13 Mar 2026 (RP done 14 Mar); 22 Jun 2026 (GN); 26 May 2026</t>
+          <t>Group 4 &amp; 27 Dec 2025, 18 Mar, 3 May, 7-8 Sep 2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>RP delivered once (14 Mar 2026). GN's 22 Jun update not seen. This tracker now serves as the master list.</t>
+          <t>RP 8 Sep: 'will sit with STDD and conclude'. Shashank &amp; Sai Sharath terminated 17 Sep (org sheet). No written conclusion to MKCD. 25 Oct: October salary strictly proportionate to performance for all telecallers - see J8.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Update this tracker's Google Sheet every Monday; email MKCD the pending list.</t>
+          <t>Send written list: who is retained / exited / on proportional pay, with data.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6192,17 +7867,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Employee Cases</t>
+          <t>Engagement, Training &amp; Culture</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Shravan: unapproved leave till 15 Oct; dependents' (driver, Rajashekar, Charan) salaries on hold - explain seriousness and responsibility; also earlier 3 leaves in Sept (ask him to meet MKCD).</t>
+          <t>Personal mobile phone restriction policy in office (lockers / deposit) - discuss with MKCD next week and implement soon.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6222,17 +7897,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Group 7 Oct 2026; Gnaneshwar 1:1 28 Sep 2026</t>
+          <t>Group 24 Oct 2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>RP called twice, no response (7 Oct). No closure.</t>
+          <t>RP: 'Sure Prabhuji'.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Report outcome of discussion with Shravan; attendance / salary decision.</t>
+          <t>Draft policy + meet MKCD week of 27 Oct.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6251,47 +7926,47 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Performance &amp; Daily Reporting</t>
+          <t>Policies &amp; Documents</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Daily login / logout time of every team member to MKCD for 10 days (pattern check of late login / early logout).</t>
+          <t>Consolidated status of ALL tasks given via WhatsApp / email / meetings (file 'Tasks 2026 - Your Name') - and weekly pending-task update email to MKCD.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Group 12 May 2026</t>
+          <t>Group 18 Aug 2025 ... 13 Mar 2026 (RP done 14 Mar); 22 Jun 2026 (GN); 26 May 2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar: 'Noted, I will share accordingly.' No delivery seen in chat.</t>
+          <t>RP delivered once (14 Mar 2026). GN's 22 Jun update not seen. This tracker now serves as the master list.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Confirm whether the 10-day log was sent; if not, send Oct 13-24 login/logout data now.</t>
+          <t>Update this tracker's Google Sheet every Monday; email MKCD the pending list.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6310,47 +7985,47 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ClickUp &amp; Daily Report Discipline</t>
+          <t>Employee Cases</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Biometric thumb access to 1st floor for Kirtaniyas, Bala Mukunda Dasa, MKCD and everyone missing.</t>
+          <t>Shravan: unapproved leave till 15 Oct; dependents' (driver, Rajashekar, Charan) salaries on hold - explain seriousness and responsibility; also earlier 3 leaves in Sept (ask him to meet MKCD).</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Group 17 Sep 2026</t>
+          <t>Group 7 Oct 2026; Gnaneshwar 1:1 28 Sep 2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar: 'tomorrow I will provide access'. No confirmation.</t>
+          <t>RP called twice, no response (7 Oct). No closure. 25 Oct: no October salary; lower package / different role on rejoining - see J3.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Confirm all staff enrolled; maintain access list.</t>
+          <t>Report outcome of discussion with Shravan; attendance / salary decision.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6369,47 +8044,47 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Work-from-home Mathaji telecaller team (Krishna-conscious ladies): Sailaja (done), G Swapna (offer 17 Oct), Vyshnavi, Malleswari, Bhavani profiles.</t>
+          <t>Replacement for Lingala Sai Sharath (donation telecaller, last working day 31 Oct) and hand-over of his positive donor leads to Sai Vardhan / Sharavan.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Group 21 Jul, 11 Aug, 8 Sep, 29 Sep, 17 Oct 2026</t>
+          <t>Claude Action Items doc (25 Oct 2026) B2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Sailaja + Swapna onboarded; others screened. Gnaneshwar's daily tasks show WFH telecaller sourcing ongoing.</t>
+          <t>Hand-over requested 15 Oct; no replacement sourced yet.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Pipeline status + performance tracking (calls/minutes/donations) for WFH callers; inform STDD/MKCD before each offer.</t>
+          <t>RP: start sourcing; GN: collect lead hand-over sheet from Sharath before 31 Oct.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6428,17 +8103,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>3 video editor cum graphic designers within 1 week.</t>
+          <t>Close the Bengaluru office and the Bengaluru telecaller position (Deva Reddy): exit date, notice, asset return, lead hand-over; update Deva Reddy's doc and the Tele-sales dept doc.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6446,29 +8121,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Group 29 Nov 2025</t>
+          <t>Claude Action Items doc A4 (with HG LKP)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1 identified from ISKCON Attapur; later Revanth (Satish referral). Satish now wants graphic designer not video editor (20 Aug).</t>
+          <t>Decision direction given 25 Oct; reverses recruitment item C11.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Confirm current open count with Satish/STDD and close.</t>
+          <t>RP: exit plan and notice draft for MKCD approval by 15 Nov.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6487,17 +8162,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>I11</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Recruit CSR Executive / Business Development Executive / Advertisement-seva sales (top priority roles listed Dec 2025).</t>
+          <t>Kanukuntla Venugopal (content writer): MKCD's view is terminate for low output (content to be AI-generated; postings moved to Venkatesh). HR to follow due process - performance record, notice.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6512,22 +8187,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Group 30 Aug 2025, 7 Dec 2025</t>
+          <t>Claude Action Items doc A5 / G3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>ClickUp 'CSR Executive Recruitment' in progress since Dec 2025; no hire.</t>
+          <t>In progress; not yet communicated to Venugopal.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Status update; decide continue / close requisition.</t>
+          <t>RP: performance record + notice draft; conclude with STDD.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6546,17 +8221,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>I12</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Executive Assistant / Executive Secretary for MKCD (experience as EA to a CXO); Rahul Bajaj profile (donor referral) to be met and opinion shared.</t>
+          <t>Org structure, department structure and a written role / designation / JD / CTC document for every person (PID39-42); lean team target &lt;= Rs 5 lakh/month; review web developer role at Rs 46k; department SPOC / role register; employee capability &amp; responsibility matrix; communicate the new structure to all staff. Oct-Dec 2026 deliverable in the People &amp; Operations plan.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6571,22 +8246,22 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Group 5 Oct 2025, 20 May 2026</t>
+          <t>Notion 'People &amp; Operations (Vertical Plan)'; ClickUp 14yp17zmek9, 14yp17zmeke, 14yp17zp7pf, 14yp17zk7xj, 14yp17zkpzz; MASTER register MA-00165</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>RP: 'I will call him &amp; meet him. Then share my opinion.' No update.</t>
+          <t>Dept R&amp;R doc and employee living docs exist (Claude Docs, 24 Oct) - JDs/CTC not yet in them.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Share outcome of Rahul Bajaj discussion; if closed, restart search.</t>
+          <t>RP: fill designation, JD and CTC for every person in the living docs; GN: capability matrix sheet.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6605,47 +8280,47 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Use Keka Hiring module (paid Rs 29,370 on 7 May 2026) for end-to-end recruitment tracking incl. interview rounds and historical data.</t>
+          <t>Satish Maddela consultancy agreement (Mondays on site; movie-editing scope, fee, IP) - pending with HR since 24 Oct. STDD to negotiate Rs 25,000/month (Rs 50,000 asked for 1-2 days a month is too costly); else end. October payment on hold. Satish -&gt; Praveen knowledge transfer and documentation.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Group 10 Mar, 7 May 2026</t>
+          <t>Claude Action Items doc B3 + G2; ClickUp 14yp17zk7xa / 14yp17zk7x9 / 14yp17zk7x6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Payment done; RP: 'within a week we can start using'. Usage not confirmed.</t>
+          <t>Agreement not drafted. Graphics lead role formally with Praveen meanwhile.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Confirm module is live; all open positions and candidates entered; share screenshot.</t>
+          <t>RP: draft agreement at the negotiated fee or issue closure letter; confirm KT completed.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6664,17 +8339,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Medical insurance: addition / deletion list to insurer (Naveen waiting for TSF Narsingi confirmation).</t>
+          <t>Roster integrity: confirm employment status of Anji (auto driver), P Ravi Kumar, Vinod Singh Thakur and the holder of the MKCP Assistant desk account (missing from the 24 Oct HR roster); also add Junjunu Mataji and Radha Giridhari records (paid but not in roster). P Ravi Kumar responsibilities / KT and the 2 pm meeting with HR to be concluded.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6682,29 +8357,29 @@
           <t>Gnaneshwar (HR Executive)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar 1:1 3 Jul 2026; ClickUp Payroll list</t>
+          <t>Claude Action Items doc B6, G14, G16; ClickUp 14yp17zmep3 / 14yp17zmep2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>No closure seen.</t>
+          <t>Roster of 42 rows (24 Oct) excludes these names.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Confirm policy renewed and all current employees covered.</t>
+          <t>GN: reconcile roster vs pay sheets of all trusts; one row per paid person.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6723,22 +8398,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Onboard Sashikanta Sahoo's wife (Janusri) as Tele Caller on payroll - CTC 18-20K; trust to be confirmed by MKCD.</t>
+          <t>Daily-report &amp; ClickUp compliance specifics: Nama Prabhu Dasa, Bala Mukunda Dasa, Banusundar irregular; Sai Vardhan to start ClickUp from 1 Nov; Revanth, Amit Mondal, Madhu Mangal, Hanumaya, Ramesh J, Purushottam, Chenna Reddy have no ClickUp / email (licence shortage) - buy licences or assign manager-maintained logs. ClickUp time tracking mandatory for all employees.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
+          <t>Gnaneshwar (HR Executive)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -6748,22 +8423,22 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Rajendra 1:1 12 Aug 2026; Group 25 Aug 2026</t>
+          <t>Claude Action Items doc B9; ClickUp 14yp17zk7xf</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'she should be on-boarded on payroll as Tele Caller, CTC and trust I will confirm'. No further update.</t>
+          <t>Licence shortage unresolved; see B2/B4.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MKCD to confirm CTC &amp; trust; HR to issue offer and onboard.</t>
+          <t>GN: licence count and cost to MKCD by 7 Nov; confirm Sai Vardhan live on ClickUp 1 Nov.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6782,22 +8457,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>I9</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Onboard Veda Vittama Dasa's wife as full-time salaried employee (trust to be confirmed by MKCD).</t>
+          <t>2026-27 recruitment plan (approx. 45 roles, approx. Rs 17.2 L/month) - re-prioritise against the budget; sequence: CSR BD manager + proposal writer, AI core team, yatra coordinators. Finalise manpower requirements per department. Tech / AI hiring (GenAI engineer, Platform lead, Data scientist, backend developer): JDs from SRRD, compensation range approval, posting, sourcing - hold until MKCD confirms priority.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
+          <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -6807,22 +8482,22 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Rajendra 1:1 / Group 21-22 Oct 2026</t>
+          <t>Claude Action Items doc B11; ClickUp 14yp17zp5xt / 5xr / 5xq / 5xp, 14yp17znrz3 / znrz1 / znryz, 14yp17zkq26 / zkq1q / zkq1r, 14yp17zmen3 / zmen2, 14yp17zmepa (CA-level accountant), MOM 86d3febu0</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'this person also can be onboarded, I will check and update which trust'.</t>
+          <t>Several duplicate hiring tasks open across ClickUp spaces; none progressing.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MKCD to confirm trust; HR to issue offer.</t>
+          <t>RP: one consolidated hiring plan sheet (role, trust, CTC, priority, status) to MKCD by 10 Nov; GN: link/merge duplicate ClickUp tasks.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6841,17 +8516,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>J12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Move Himanshu and Accountant Naveen V from TSF to another trust from 1 Oct 2026 (TSF has no operations).</t>
+          <t>CONFIDENTIAL (MKCD + RP only): Gnaneshwar - termination for underperformance over many months to be discussed with HR Manager; document the performance record; confirm consistency with offer-letter terms and put in writing before the October payroll (5 Nov).</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6859,29 +8534,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Group 29 Sep, 10 Oct 2026</t>
+          <t>Claude Action Items doc G1; Gnaneshwar living doc 25 Oct note</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Naveen V shifted to RGIL (email 10 Oct). Himanshu - no confirmation (org sheet suggests HKM India).</t>
+          <t>Not yet discussed with RP.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Confirm Himanshu's transfer and effective date.</t>
+          <t>MKCD + RP meeting before 5 Nov. Deliberately NOT created in ClickUp.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6889,28 +8564,24 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Share copies of all RGI appointment letters with MKCD, including MKCD's own appointment letter.</t>
+          <t>Vikash Kumar (Senior Tele Sales Executive): flagged non-performer 4-5 months; did not attend in October - no October salary; on return salary proportionate to performance. Performance plan or exit.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6918,29 +8589,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Group 9 Feb 2026</t>
+          <t>Claude Action Items doc B1, G21</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'share me the copies... even in my name one appointment letter should be there, I have not yet received'. No confirmation.</t>
+          <t>Earlier: WFH till Diwali (see H4).</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Share folder link with all RGI appointment letters.</t>
+          <t>RP: apply in October pay sheet; written notice.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6959,47 +8630,47 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>All employees' personal documents (Aadhaar, PAN, blood group, emergency contacts) in a Google Drive folder, link shared with MKCD.</t>
+          <t>B Sharavan Kumar: no October salary (absent all month, no leave balance); on rejoining a lower package and different role for a few months.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Group 22 &amp; 26 Oct 2025</t>
+          <t>Claude Action Items doc G10 (see H1)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>RP: 'once collected fully, will be shared on Google Drive'. Link never seen in chat.</t>
+          <t>Unapproved leave since early Oct.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Share Drive folder link; keep updated for every new joiner.</t>
+          <t>RP: pay sheet entry + letter.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7018,17 +8689,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sunday &amp; holiday roster for the whole year (50% telecallers + 1 graphics person every Sunday), finalised monthly with staff.</t>
+          <t>Prema Rupa Dasa: no October salary (no performance for approx. 2 years despite warnings); rejoin only in a new role at a revised lower CTC - perform or exit.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7043,22 +8714,22 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Group 20 Dec 2025, 10 Jan, 3 Mar 2026</t>
+          <t>Claude Action Items doc G12 (with Suguna Radha DD; see H3)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>RP 3 Mar: 'spoke to 2 telecallers, will formalise'. Yearly roster never shared.</t>
+          <t>Discussion with MKCD on 16 Oct.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Share annual roster (Nov 2026 - Oct 2027) in Google Sheet.</t>
+          <t>RP: pay sheet entry + revised-role letter.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7077,47 +8748,43 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ratha Yatra 2026 expenses: collect ALL bills; deduct from salary where bills missing; final consolidated report in Google Sheet with all latest payments.</t>
+          <t>Purushottam Sharma: stop salary - 1-1.5 months' leave taken without approval despite written refusal; resumes only on rejoining.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar 1:1 29 Jul - 18 Aug 2026</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Bill-status report shared 7-8 Aug (Excel). Sai Vardhan still had a few bills pending; final Google Sheet after 18 Aug payments not seen.</t>
-        </is>
-      </c>
+          <t>Claude Action Items doc G25</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Share final Google Sheet; confirm Sai Vardhan bills closed or deducted.</t>
+          <t>RP: pay sheet entry + letter.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7136,17 +8803,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hem Chand variable pay Rs 50,000 approved - pay with September salary.</t>
+          <t>Kouloju Sumanth (SEO): terminate - no performance for weeks/months, excessive leave, conduct. Hem Chand takes over SEO.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7154,29 +8821,25 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Group 6 Oct 2026</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Approved by MKCD &amp; STDD 6 Oct. Payment not confirmed in chat.</t>
-        </is>
-      </c>
+          <t>Claude Action Items doc G6</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Confirm paid.</t>
+          <t>RP: termination due process with Hem Chand; final settlement.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -7195,17 +8858,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Arjun: recover Rs 10,000 advance (Dec 2025) before 5 Apr 2026; email on record about non-response and pending bills; salary hold until settlement.</t>
+          <t>Written serious warnings: Hem Chand Tunga (targets not taken seriously; clear months-old pending tasks or salary cut), Sonayla Sudhakar (salary proportionate to performance from October), Nagella Banusundar / Arjuna Bandhu Dasa (no log-in/log-out, no ClickUp, tasks pending; report at 10 am; must do tele-sales; training-attendance issue), Radha Giridhari (October salary cut with warning; behaviour must change).</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7213,29 +8876,25 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Group 4 Mar, 23 Mar, 26 Mar 2026</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>RP 'Ok Prabhuji'. Arjun still unresponsive in Oct (13 Oct). No closure.</t>
-        </is>
-      </c>
+          <t>Claude Action Items doc G5, G23, G20, G16; ClickUp 14yp17zp0mj</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Confirm recovery and email trail.</t>
+          <t>RP: four warning letters by 3 Nov; copies to MKCD.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -7254,17 +8913,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>J9</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Vineet Bulbule group (KMY batch): clear 100% pending payment; escalate via Shruthadev Prabhu if needed.</t>
+          <t>End consultant retainers of Aniket (DYGN Media) and Srinivas Mahankali immediately; redirect the cost to in-house full-time hires.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7272,29 +8931,25 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Rajendra 1:1 25 Jun, 1 Jul, 7 Aug 2026</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>RP tried twice (25 Jun); MKCD chased again 7 Aug. No closure.</t>
-        </is>
-      </c>
+          <t>Claude Action Items doc G26 (with STDD)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Confirm with Accountant Naveen that balance is received; else escalate.</t>
+          <t>RP: closure emails and final invoices; inform Finance.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -7313,27 +8968,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; Finance</t>
+          <t>Performance &amp; Daily Reporting</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Satish: attendance full till 19 Sep; leave 20-30 Sep adjusted from EL (mail to Achyuth); resignation accepted; now consultant - trust to be confirmed by MKCD (likely HKM Hyd).</t>
+          <t>Daily login / logout time of every team member to MKCD for 10 days (pattern check of late login / early logout).</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7343,17 +8998,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar 1:1 28 Sep 2026; Rajendra 1:1 30 Sep, 22 Oct 2026</t>
+          <t>Group 12 May 2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'I will update after 2 days. Mostly Satish will be consultant in HKM Hyderabad trust'.</t>
+          <t>Gnaneshwar: 'Noted, I will share accordingly.' No delivery seen in chat.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MKCD confirms trust; HR issues consultant agreement; confirm EL adjustment mail sent.</t>
+          <t>Confirm whether the 10-day log was sent; if not, send Oct 13-24 login/logout data now.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -7372,27 +9027,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Engagement, Training &amp; Culture</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Extra Mile / Best Performer award: nominations by 10th, finalised by 14th, ceremony on 15th every month with data-backed performance review; Q2 (Jul-Sep) awards in 2nd week Oct.</t>
+          <t>Work-from-home Mathaji telecaller team (Krishna-conscious ladies): Sailaja (done), G Swapna (offer 17 Oct), Vyshnavi, Malleswari, Bhavani profiles.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7402,17 +9057,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Group 14 Feb, 15 Apr, 12 May, 27 Sep 2026</t>
+          <t>Group 21 Jul, 11 Aug, 8 Sep, 29 Sep, 17 Oct 2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Held Mar, Apr, May. Q2 awards pending - MKCD wants performance report first (27 Sep).</t>
+          <t>Sailaja + Swapna onboarded; others screened. Gnaneshwar's daily tasks show WFH telecaller sourcing ongoing.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Run Q2 awards once A4 report is ready; auto driver Venkatesh (14 yrs) to be recognised.</t>
+          <t>Pipeline status + performance tracking (calls/minutes/donations) for WFH callers; inform STDD/MKCD before each offer.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -7431,17 +9086,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Engagement, Training &amp; Culture</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2-day team-building training for whole organisation + 1-day recap after a month (announced by RP 26 Jun).</t>
+          <t>3 video editor cum graphic designers within 1 week.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -7449,9 +9104,9 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7461,17 +9116,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Group 26 Jun 2026</t>
+          <t>Group 29 Nov 2025</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Not scheduled.</t>
+          <t>1 identified from ISKCON Attapur; later Revanth (Satish referral). Satish now wants graphic designer not video editor (20 Aug).</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Propose dates, trainer, agenda, budget.</t>
+          <t>Confirm current open count with Satish/STDD and close.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -7490,17 +9145,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Policies &amp; Documents</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Tour &amp; Travel / Yatra employee allowance policy (Rs 750 food/day, official accommodation, 3AC train, medical via ESI/insurance, nothing else) - finalise, get approval and circulate to all Yatra employees.</t>
+          <t>Recruit CSR Executive / Business Development Executive / Advertisement-seva sales (top priority roles listed Dec 2025).</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -7520,17 +9175,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Group 11 Sep 2025, 5 Oct 2025, 30 Oct 2025</t>
+          <t>Group 30 Aug 2025, 7 Dec 2025</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>v1 sent by email 29 Oct 2025; RP asked MKCD to review. Not confirmed as approved / circulated.</t>
+          <t>ClickUp 'CSR Executive Recruitment' in progress since Dec 2025; no hire. Also ClickUp 14yp17zmepb (BDM recruitment).</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MKCD to approve; RP to circulate with acknowledgement from each Yatra employee before next yatra.</t>
+          <t>Status update; decide continue / close requisition.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -7549,17 +9204,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Employee Cases</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Sachi: fixed office hours (11:00 or 11:30 start, 8.5 hrs), no Sundays, no late nights - communicate as final decision.</t>
+          <t>Executive Assistant / Executive Secretary for MKCD (experience as EA to a CXO); Rahul Bajaj profile (donor referral) to be met and opinion shared.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -7567,9 +9222,9 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -7579,17 +9234,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Group 27 Sep 2026</t>
+          <t>Group 5 Oct 2025, 20 May 2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>No confirmation.</t>
+          <t>RP: 'I will call him &amp; meet him. Then share my opinion.' No update.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Confirm communicated and followed.</t>
+          <t>Share outcome of Rahul Bajaj discussion; if closed, restart search.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7608,27 +9263,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Employee Cases</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Premroop Prabhu, Sudhakar, Sahoo - discussion with MKCD on 16 Oct; outcomes / actions to be recorded.</t>
+          <t>Use Keka Hiring module (paid Rs 29,370 on 7 May 2026) for end-to-end recruitment tracking incl. interview rounds and historical data.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -7638,17 +9293,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Rajendra 1:1 16 Oct 2026</t>
+          <t>Group 10 Mar, 7 May 2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Meeting held 16 Oct; no written outcome.</t>
+          <t>Payment done; RP: 'within a week we can start using'. Usage not confirmed.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Email summary of decisions and actions for each.</t>
+          <t>Confirm module is live; all open positions and candidates entered; share screenshot.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7667,27 +9322,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Employee Cases</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar's own salary discussion request (23 Sep) and Daily Performance Report meeting with MKCD + STDD + RP (18 Sep).</t>
+          <t>Medical insurance: addition / deletion list to insurer (Naveen waiting for TSF Narsingi confirmation).</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MKCD (your own action)</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -7697,17 +9352,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar 1:1 18 &amp; 23 Sep 2026</t>
+          <t>Gnaneshwar 1:1 3 Jul 2026; ClickUp Payroll list</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'not today'. Not scheduled.</t>
+          <t>No closure seen.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MKCD to schedule 30-min slot.</t>
+          <t>Confirm policy renewed and all current employees covered.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -7715,54 +9370,58 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ClickUp &amp; Daily Report Discipline</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Try Truein AI time-capture tool for attendance.</t>
+          <t>Onboard Sashikanta Sahoo's wife (Janusri) as Tele Caller on payroll - CTC 18-20K; trust to be confirmed by MKCD.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Group 22 May 2026</t>
+          <t>Rajendra 1:1 12 Aug 2026; Group 25 Aug 2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>'Noted Prabhu.' No follow-up.</t>
+          <t>MKCD: 'she should be on-boarded on payroll as Tele Caller, CTC and trust I will confirm'. No further update. 25 Oct: MKCD prefers event-based consultant for Junjunu Mataji instead of full-time - see J10.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Confirm whether trial was done; share 3-line finding.</t>
+          <t>MKCD to confirm CTC &amp; trust; HR to issue offer and onboard.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -7781,47 +9440,47 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Evaluate Jayanti Achuta Narayan Rao (Accounts, referred by Bhanu Nitai Prabhu) and give feedback.</t>
+          <t>Onboard Veda Vittama Dasa's wife as full-time salaried employee (trust to be confirmed by MKCD).</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad (HR Manager)</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Group 24 Sep 2026</t>
+          <t>Rajendra 1:1 / Group 21-22 Oct 2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>STDD said profile too senior; Bhanu Prabhu asked for full evaluation.</t>
+          <t>MKCD: 'this person also can be onboarded, I will check and update which trust'.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Close the loop with Bhanu Nitai Prabhu and STDD.</t>
+          <t>MKCD to confirm trust; HR to issue offer.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -7840,17 +9499,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Aptitude / psychometric / English tests for all new candidates; share test details used so far.</t>
+          <t>Move Himanshu and Accountant Naveen V from TSF to another trust from 1 Oct 2026 (TSF has no operations).</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -7858,29 +9517,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Group 21 Oct 2025; ClickUp list 'Rajendra Prasad'</t>
+          <t>Group 29 Sep, 10 Oct 2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>RP: 'I will check &amp; share my feedback.' ClickUp item still 'to do'.</t>
+          <t>Naveen V shifted to RGIL (email 10 Oct). Himanshu - no confirmation (org sheet suggests HKM India). 25 Oct: Himanshu move approved 12 Oct; payroll + PF paperwork pending - see J11.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Finalise test set and add to the 4-round SOP.</t>
+          <t>Confirm Himanshu's transfer and effective date.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -7899,17 +9558,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Onboarding, Trusts &amp; Statutory</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Solution to stop new hires leaving right after first salary (bond rejected by RP) - propose alternative (notice-period clause, salary-hold, probation terms).</t>
+          <t>Share copies of all RGI appointment letters with MKCD, including MKCD's own appointment letter.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -7917,29 +9576,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Group 4 &amp; 7 Dec 2025</t>
+          <t>Group 9 Feb 2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'Then what is the solution...?' - no answer.</t>
+          <t>MKCD: 'share me the copies... even in my name one appointment letter should be there, I have not yet received'. No confirmation.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Written proposal to MKCD.</t>
+          <t>Share folder link with all RGI appointment letters.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -7958,7 +9617,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -7968,12 +9627,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RGIL email IDs for all staff (Hem Chand to create).</t>
+          <t>All employees' personal documents (Aadhaar, PAN, blood group, emergency contacts) in a Google Drive folder, link shared with MKCD.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
+          <t>Rajendra Prasad + Gnaneshwar</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -7983,22 +9642,22 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Rajendra 1:1 29 Aug 2026</t>
+          <t>Group 22 &amp; 26 Oct 2025</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>MKCD told Hem Chand to create for all staff. No confirmation.</t>
+          <t>RP: 'once collected fully, will be shared on Google Drive'. Link never seen in chat.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Confirm creation and share ID list.</t>
+          <t>Share Drive folder link; keep updated for every new joiner.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -8017,47 +9676,47 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Office systems requirement: Rajashekhar Reddy, Shiva Vara Prasad, Sudhakar need new systems; Sathish to return TSF Mac mini/monitor; follow up with others.</t>
+          <t>Sunday &amp; holiday roster for the whole year (50% telecallers + 1 graphics person every Sunday), finalised monthly with staff.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar (HR Executive)</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Gnaneshwar 1:1 20 Aug 2026</t>
+          <t>Group 20 Dec 2025, 10 Jan, 3 Mar 2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'Yes'. No closure seen.</t>
+          <t>RP 3 Mar: 'spoke to 2 telecallers, will formalise'. Yearly roster never shared.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Confirm systems issued / TSF equipment returned.</t>
+          <t>Share annual roster (Nov 2026 - Oct 2027) in Google Sheet.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -8076,17 +9735,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Onboarding, Trusts &amp; Statutory</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ID cards for all employees who do not have one (needed for festival duty).</t>
+          <t>Ratha Yatra 2026 expenses: collect ALL bills; deduct from salary where bills missing; final consolidated report in Google Sheet with all latest payments.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -8094,29 +9753,29 @@
           <t>Gnaneshwar (HR Executive)</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Group 25 Aug 2026</t>
+          <t>Gnaneshwar 1:1 29 Jul - 18 Aug 2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>'Noted sir.' No completion update.</t>
+          <t>Bill-status report shared 7-8 Aug (Excel). Sai Vardhan still had a few bills pending; final Google Sheet after 18 Aug payments not seen.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Confirm list and issuance.</t>
+          <t>Share final Google Sheet; confirm Sai Vardhan bills closed or deducted.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -8135,22 +9794,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Engagement, Training &amp; Culture</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Watch APF HR symposium recording (Golden Habits, TAPF Way) and share notes of what can be implemented.</t>
+          <t>Hem Chand variable pay Rs 50,000 approved - pay with September salary.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad + Gnaneshwar</t>
+          <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -8160,22 +9819,22 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Group 10 &amp; 12 Jul 2026</t>
+          <t>Group 6 Oct 2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>RP: 'Ok'. Notes not seen.</t>
+          <t>Approved by MKCD &amp; STDD 6 Oct. Payment not confirmed in chat.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Send notes (1 page).</t>
+          <t>Confirm paid.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -8194,17 +9853,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Engagement, Training &amp; Culture</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Collect participant feedback on 28-29 Jun sales training (Arjun's feedback shared); keep feedback window open.</t>
+          <t>Arjun: recover Rs 10,000 advance (Dec 2025) before 5 Apr 2026; email on record about non-response and pending bills; salary hold until settlement.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -8219,22 +9878,22 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Group 29 Jun 2026</t>
+          <t>Group 4 Mar, 23 Mar, 26 Mar 2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Not seen.</t>
+          <t>RP 'Ok Prabhuji'. Arjun still unresponsive in Oct (13 Oct). No closure.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Share feedback summary.</t>
+          <t>Confirm recovery and email trail.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -8242,24 +9901,28 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Policies &amp; Documents</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Mobile recharge policy (decent calling + data pack).</t>
+          <t>Vineet Bulbule group (KMY batch): clear 100% pending payment; escalate via Shruthadev Prabhu if needed.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -8274,22 +9937,22 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Group 5 Oct 2025</t>
+          <t>Rajendra 1:1 25 Jun, 1 Jul, 7 Aug 2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>RP said he will create. Not seen.</t>
+          <t>RP tried twice (25 Jun); MKCD chased again 7 Aug. No closure.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Share policy.</t>
+          <t>Confirm with Accountant Naveen that balance is received; else escalate.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -8308,17 +9971,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Policies &amp; Documents</t>
+          <t>Payroll &amp; Finance</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Map each telecaller to 1-2 preachers for knowledge transfer.</t>
+          <t>Satish: attendance full till 19 Sep; leave 20-30 Sep adjusted from EL (mail to Achyuth); resignation accepted; now consultant - trust to be confirmed by MKCD (likely HKM Hyd).</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -8326,29 +9989,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Group 17 Sep 2025</t>
+          <t>Gnaneshwar 1:1 28 Sep 2026; Rajendra 1:1 30 Sep, 22 Oct 2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'Please do mapping immediately'. No mapping shared.</t>
+          <t>MKCD: 'I will update after 2 days. Mostly Satish will be consultant in HKM Hyderabad trust'. Consultancy agreement and KT still open - see I2.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Share mapping sheet (may be superseded by Sai Vardhan structure).</t>
+          <t>MKCD confirms trust; HR issues consultant agreement; confirm EL adjustment mail sent.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -8367,17 +10030,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Policies &amp; Documents</t>
+          <t>Engagement, Training &amp; Culture</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Certificate format for awards - finalise (printing for 1 year).</t>
+          <t>Extra Mile / Best Performer award: nominations by 10th, finalised by 14th, ceremony on 15th every month with data-backed performance review; Q2 (Jul-Sep) awards in 2nd week Oct.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -8385,29 +10048,29 @@
           <t>Rajendra Prasad (HR Manager)</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Group 27 Feb - 2 Mar 2026</t>
+          <t>Group 14 Feb, 15 Apr, 12 May, 27 Sep 2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>MKCD: 'we'll finalise next week'. Not seen.</t>
+          <t>Held Mar, Apr, May. Q2 awards pending - MKCD wants performance report first (27 Sep).</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Confirm.</t>
+          <t>Run Q2 awards once A4 report is ready; auto driver Venkatesh (14 yrs) to be recognised.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -8415,9 +10078,1641 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Engagement, Training &amp; Culture</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2-day team-building training for whole organisation + 1-day recap after a month (announced by RP 26 Jun).</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Group 26 Jun 2026</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Not scheduled.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Propose dates, trainer, agenda, budget.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Policies &amp; Documents</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Tour &amp; Travel / Yatra employee allowance policy (Rs 750 food/day, official accommodation, 3AC train, medical via ESI/insurance, nothing else) - finalise, get approval and circulate to all Yatra employees.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Group 11 Sep 2025, 5 Oct 2025, 30 Oct 2025</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>v1 sent by email 29 Oct 2025; RP asked MKCD to review. Not confirmed as approved / circulated.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>MKCD to approve; RP to circulate with acknowledgement from each Yatra employee before next yatra.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Employee Cases</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Sachi: fixed office hours (11:00 or 11:30 start, 8.5 hrs), no Sundays, no late nights - communicate as final decision.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Group 27 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>No confirmation.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Confirm communicated and followed.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Employee Cases</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Premroop Prabhu, Sudhakar, Sahoo - discussion with MKCD on 16 Oct; outcomes / actions to be recorded.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra 1:1 16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Meeting held 16 Oct; no written outcome. 25 Oct decisions recorded in J4 (Prema Rupa), J7 (Sudhakar), J10 (Sashikanta).</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Email summary of decisions and actions for each.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Employee Cases</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar's own salary discussion request (23 Sep) and Daily Performance Report meeting with MKCD + STDD + RP (18 Sep).</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar 1:1 18 &amp; 23 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>MKCD: 'not today'. Not scheduled.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>MKCD to schedule 30-min slot.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>I13</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Backup employee for every role with knowledge-transfer plan (PID101); second-line names to confirm (Tele-sales, Yatra coordinator, ERP, accounts lead).</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Notion People &amp; Operations plan PID101; Claude Action Items doc B12</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>RP: backup column in the roster sheet, confirmed with each department head.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end recruitment &amp; onboarding SOP and onboarding kit (PID102); quarterly training calendar with in-house and external speakers (PID15/16, Jan-Mar 2027); written R&amp;R for Culture Connect; incorporate the GM/AVP promotion qualifying-criteria resolution into a formal promotion policy; re-recruit trained ex-employees under stricter SOPs where suitable.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Notion People &amp; Operations plan; ClickUp 14yp17znrx6; MASTER register MA-02102, MA-01735</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Planning stage.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>RP: SOP + promotion policy drafts to MKCD by 10 Nov; training calendar by Dec.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Employee monitoring software (laptops PID13, field executives PID14): trial and disclosure decision. Move performance-review ownership from HR to Operations (decision) and build the live performance dashboard.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp 14yp17zmepj, 14yp17znrwb, 14yp17znrwc; Notion PID13/14</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Decisions pending with MKCD.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision; GN to run the trial once approved.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>I16</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Email all staff on office hours, Sunday working and discipline rules (after-hours / spiritual-course time is not office hours; report at 10 am). Puri staff pilgrimage dates to be fixed with HR Manager. Prasadam contamination complaint to be closed with HR Manager.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp 14yp17zmep1, 14yp17zp0mr, 14yp17zp0mk</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Open in Arjun Prabhu / MKCP Assistant lists.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>RP: one circular on hours &amp; discipline; dates for Puri pilgrimage; complaint closure note.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Social-media executive vacancy (Akhil left 17 Oct) - now covered by Venkatesh (PPC). MKCD to decide whether to still hire; HR to close or open the requisition accordingly. Akhil PIP task in ClickUp is obsolete - close it.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B4 / A5; ClickUp 14yp17zmenz (Akhil PIP)</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Sep-2026 plan listed a Social Media Manager.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision by 15 Nov; GN to close ClickUp task 14yp17zmenz.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Settle department placement of Sashikanta Sahoo, Prema Rupa Dasa, Sonayla Sudhakar, Yankiral Shiv Raj, Purushottam Sharma, P Srilakshmi Sailaja, Gaddam Sai Kiran (sources disagree); record accountant V Naveen Kumar as Yatra dept (TRIDAS/TSF accounts) or Hanuma's transfer to Yatra once HG LKP agrees. Then update master roster, Whimsical org board and department docs.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B7, A1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>MKCD + STDD decision pending (due 7 Nov).</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>RP: prepare the placement sheet with recommendation for MKCD/STDD; GN: update roster/docs after decision.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Decide which HR notes (performance flags) stay in the shared employee living documents vs a private HR tab.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>MKCD (your own action)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B10</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Docs are shareable; performance notes currently inside them.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>MKCD decision; RP to then move confidential notes.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Sashikanta Sahoo: fix R&amp;R in writing (housekeeping, purchases/stores/warehouse, kirtan-training organisation, watering plants - weekly duties - plus daily fundraising / telecalling and family visits). Junjunu Mataji (his wife): solid roadmap or move to event-based consultant paid per event (preferred) - supersedes the full-time telecaller onboarding in D12.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc G13, G14 (with Suguna Radha DD)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>RP: written R&amp;R letter for Sashikanta; consultant terms for Junjunu Mataji for MKCD approval.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>J - October payroll &amp; performance decisions (MKCD 25 Oct)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Himanshu Bisoyi trust movement TSF -&gt; HKM Hyderabad (approved 12 Oct): complete payroll and PF paperwork (no new budget).</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B5 (see D2)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>RP: new appointment letter + PF transfer with Finance by 31 Oct.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp &amp; Daily Report Discipline</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Try Truein AI time-capture tool for attendance.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Group 22 May 2026</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>'Noted Prabhu.' No follow-up.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Confirm whether trial was done; share 3-line finding.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Evaluate Jayanti Achuta Narayan Rao (Accounts, referred by Bhanu Nitai Prabhu) and give feedback.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Group 24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>STDD said profile too senior; Bhanu Prabhu asked for full evaluation.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Close the loop with Bhanu Nitai Prabhu and STDD.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude / psychometric / English tests for all new candidates; share test details used so far.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Group 21 Oct 2025; ClickUp list 'Rajendra Prasad'</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>RP: 'I will check &amp; share my feedback.' ClickUp item still 'to do'.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Finalise test set and add to the 4-round SOP.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Solution to stop new hires leaving right after first salary (bond rejected by RP) - propose alternative (notice-period clause, salary-hold, probation terms).</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Group 4 &amp; 7 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>MKCD: 'Then what is the solution...?' - no answer.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Written proposal to MKCD.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding, Trusts &amp; Statutory</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>RGIL email IDs for all staff (Hem Chand to create).</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra 1:1 29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>MKCD told Hem Chand to create for all staff. No confirmation.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Confirm creation and share ID list.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding, Trusts &amp; Statutory</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Office systems requirement: Rajashekhar Reddy, Shiva Vara Prasad, Sudhakar need new systems; Sathish to return TSF Mac mini/monitor; follow up with others.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar 1:1 20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>MKCD: 'Yes'. No closure seen.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Confirm systems issued / TSF equipment returned.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding, Trusts &amp; Statutory</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>ID cards for all employees who do not have one (needed for festival duty).</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Group 25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>'Noted sir.' No completion update.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Confirm list and issuance.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Engagement, Training &amp; Culture</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Watch APF HR symposium recording (Golden Habits, TAPF Way) and share notes of what can be implemented.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad + Gnaneshwar</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Group 10 &amp; 12 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>RP: 'Ok'. Notes not seen.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Send notes (1 page).</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Engagement, Training &amp; Culture</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Collect participant feedback on 28-29 Jun sales training (Arjun's feedback shared); keep feedback window open.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Group 29 Jun 2026</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Not seen.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Share feedback summary.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Policies &amp; Documents</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Mobile recharge policy (decent calling + data pack).</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Group 5 Oct 2025</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>RP said he will create. Not seen.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Share policy.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Policies &amp; Documents</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Map each telecaller to 1-2 preachers for knowledge transfer.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Group 17 Sep 2025</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>MKCD: 'Please do mapping immediately'. No mapping shared.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Share mapping sheet (may be superseded by Sai Vardhan structure).</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Policies &amp; Documents</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Certificate format for awards - finalise (printing for 1 year).</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad (HR Manager)</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Group 27 Feb - 2 Mar 2026</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>MKCD: 'we'll finalise next week'. Not seen.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Confirm.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Verify and close stale HR tasks: Shashank termination notice (14yp17zmeny), TSF salary payments release (14yp17znrw1), PF withdrawal rules query from a kirtaniya (MASTER MA-00317), staff engagement planning review (MA-00919), volunteer details collection (MOM 86d3febpm).</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>ClickUp MKCP Assistant list; MOM lists; MASTER register</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Status unknown; likely done or obsolete.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>GN: confirm each and close in ClickUp with a one-line comment.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>I - Sweep: Claude Action Items / ClickUp / Notion / MASTER register</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Collect dates of joining for all staff from Keka / GreytHR into the employee living documents (only 4 confirmed) and link every employee living doc from the Notion Leadership Hub and the HR roster sheet.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Gnaneshwar (HR Executive)</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Claude Action Items doc B8, D3</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>GN: export DOJ list from Keka; add to each doc; add links column in roster sheet.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8556,7 +11851,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Policy stated repeatedly; telecaller proportional pay applied partly (Apr-May). Not yet systematic for all employees.</t>
+          <t>Policy stated repeatedly; telecaller proportional pay applied partly (Apr-May). Not yet systematic for all employees. Also ClickUp 14yp17zmem1 (performance-linked pay one-to-one).</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -9098,7 +12393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9374,44 +12669,44 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+          <t>Gnaneshwar - HR Executive (permanent / recurring responsibilities)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Performance Management System owner</t>
+          <t>Roster integrity &amp; employee living documents</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Written targets for every employee (with reporting authorities); monthly appraisal; half-yearly and annual (March-April) cycle; salary proportional to performance; selection and rollout of an appraisal software.</t>
+          <t>Every person paid on any trust appears in the HR roster with department, designation, date of joining, trust and a linked employee living document; reconcile roster vs pay sheets every month; link docs from the Notion Leadership Hub.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As required</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+          <t>Gnaneshwar - HR Executive (permanent / recurring responsibilities)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Recruitment pipeline owner</t>
+          <t>ClickUp hygiene across spaces</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tele Sales Manager, PPC expert, Digital Marketing Manager, CSR / BDE and other approved roles; mandatory 4-round process (HR -&gt; STDD -&gt; MHBD -&gt; MKCD); inform MKCD &amp; STDD before every offer letter; aptitude / psychometric tests; Keka Hiring module.</t>
+          <t>Weekly: close or merge duplicate / obsolete HR tasks in all ClickUp spaces (MKCP Assistant, Arjun Prabhu, MOM lists) and keep one live HR follow-up list.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>As required</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -9423,12 +12718,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Payroll &amp; statutory</t>
+          <t>Performance Management System owner</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Pay sheets of all trusts to MKCD by 4th; incentives / variable pay included; monthly attendance to each employee before payroll; PF / ESI challans; salary advances and recoveries; consultant invoices.</t>
+          <t>Written targets for every employee (with reporting authorities); monthly appraisal; half-yearly and annual (March-April) cycle; salary proportional to performance; selection and rollout of an appraisal software.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -9445,12 +12740,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Trust structure &amp; onboarding</t>
+          <t>Recruitment pipeline owner</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Every employee / consultant on the correct trust as per MKCD's list; offer / appointment letters; RGI compliance; copies of letters to MKCD.</t>
+          <t>Tele Sales Manager, PPC expert, Digital Marketing Manager, CSR / BDE and other approved roles; mandatory 4-round process (HR -&gt; STDD -&gt; MHBD -&gt; MKCD); inform MKCD &amp; STDD before every offer letter; aptitude / psychometric tests; Keka Hiring module.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -9467,17 +12762,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Policies</t>
+          <t>Payroll &amp; statutory</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Tour &amp; Travel / Yatra allowance, mobile recharge, mobile-phone-at-work, Sunday &amp; holiday annual roster, leave approvals, office hours, escalation discipline, non-performer exit with STDD.</t>
+          <t>Pay sheets of all trusts to MKCD by 4th; incentives / variable pay included; monthly attendance to each employee before payroll; PF / ESI challans; salary advances and recoveries; consultant invoices.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>As required</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -9489,17 +12784,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Rewards &amp; Recognition</t>
+          <t>Trust structure &amp; onboarding</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Extra Mile award on 15th of every month with data-backed review; quarterly awards; monthly team meeting with snacks prasadam.</t>
+          <t>Every employee / consultant on the correct trust as per MKCD's list; offer / appointment letters; RGI compliance; copies of letters to MKCD.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As required</t>
         </is>
       </c>
     </row>
@@ -9511,12 +12806,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Training &amp; development</t>
+          <t>Policies</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Induction for new joiners; sales / team-building programs with recording, feedback and certificates; implement learnings from HR symposiums.</t>
+          <t>Tour &amp; Travel / Yatra allowance, mobile recharge, mobile-phone-at-work, Sunday &amp; holiday annual roster, leave approvals, office hours, escalation discipline, non-performer exit with STDD.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -9533,17 +12828,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Reporting to management</t>
+          <t>Rewards &amp; Recognition</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MoM after every management meeting; monthly HR dashboard (headcount, attrition, attendance, performance, recruitment status); weekly pending-task status with Gnaneshwar.</t>
+          <t>Extra Mile award on 15th of every month with data-backed review; quarterly awards; monthly team meeting with snacks prasadam.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -9555,17 +12850,149 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>Training &amp; development</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Induction for new joiners; sales / team-building programs with recording, feedback and certificates; implement learnings from HR symposiums.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Reporting to management</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>MoM after every management meeting; monthly HR dashboard (headcount, attrition, attendance, performance, recruitment status); weekly pending-task status with Gnaneshwar.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>Availability</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>HR Manager or HR Executive present in office during the 1st week of every month (payroll week); no simultaneous leave.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Written warnings before payroll</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Every non-performance / target-shortfall / unapproved-absence case gets a written warning email before the month's payroll, with the salary consequence stated; copies filed in the employee file and a list sent to MKCD.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Exits, consultants &amp; trust movements - due process</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Performance record, notice, final settlement and letters for every exit; written consultancy agreements (scope, fee, IP, days on site); appointment letters and PF paperwork for every trust movement.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Organisation structure &amp; JD document owner</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Maintain the department R&amp;R documents and employee living documents: designation, JD, CTC and reporting line for every person (PID39-42); backup person and KT plan for every role (PID101); communicate structure changes to all staff.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad - HR Manager (permanent / recurring responsibilities)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Policies &amp; SOP library for HR</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment &amp; onboarding SOP, promotion policy, office-hours / Sunday / discipline circular, employee-monitoring disclosure; quarterly training calendar (PID15/16).</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>As required</t>
         </is>
       </c>
     </row>
